--- a/output/topology_excel/14757.xlsx
+++ b/output/topology_excel/14757.xlsx
@@ -425,58 +425,38 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>房间1</t>
+          <t>RoomA</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>类型1</t>
+          <t>RoomB</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>面积1</t>
+          <t>ConnectionType</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>房间2</t>
+          <t>Count</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>类型2</t>
+          <t>Length</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>面积2</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>连接类型</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>数量</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>length</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>width</t>
+          <t>Width</t>
         </is>
       </c>
     </row>
@@ -484,37 +464,21 @@
       <c r="A2" t="n">
         <v>2</v>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>230730</v>
+      <c r="B2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E2" t="n">
+        <v>82</v>
       </c>
       <c r="F2" t="n">
-        <v>87980</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>门</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I2" t="n">
-        <v>82</v>
-      </c>
-      <c r="J2" t="n">
         <v>11</v>
       </c>
     </row>
@@ -522,37 +486,21 @@
       <c r="A3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>230730</v>
+      <c r="B3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E3" t="n">
+        <v>84</v>
       </c>
       <c r="F3" t="n">
-        <v>43400</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>门</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I3" t="n">
-        <v>84</v>
-      </c>
-      <c r="J3" t="n">
         <v>11</v>
       </c>
     </row>
@@ -560,37 +508,21 @@
       <c r="A4" t="n">
         <v>2</v>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>230730</v>
+      <c r="B4" t="n">
+        <v>5</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
       </c>
       <c r="D4" t="n">
-        <v>5</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E4" t="n">
+        <v>91</v>
       </c>
       <c r="F4" t="n">
-        <v>23256</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>门</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" t="n">
-        <v>91</v>
-      </c>
-      <c r="J4" t="n">
         <v>11</v>
       </c>
     </row>
@@ -598,37 +530,21 @@
       <c r="A5" t="n">
         <v>4</v>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>43400</v>
+      <c r="B5" t="n">
+        <v>6</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
       </c>
       <c r="D5" t="n">
-        <v>6</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E5" t="n">
+        <v>63</v>
       </c>
       <c r="F5" t="n">
-        <v>23664</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>门</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I5" t="n">
-        <v>63</v>
-      </c>
-      <c r="J5" t="n">
         <v>11</v>
       </c>
     </row>
@@ -636,37 +552,21 @@
       <c r="A6" t="n">
         <v>1</v>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>18912</v>
+      <c r="B6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E6" t="n">
+        <v>96</v>
       </c>
       <c r="F6" t="n">
-        <v>87980</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I6" t="n">
-        <v>96</v>
-      </c>
-      <c r="J6" t="n">
         <v>30</v>
       </c>
     </row>
@@ -674,37 +574,21 @@
       <c r="A7" t="n">
         <v>2</v>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>230730</v>
+      <c r="B7" t="n">
+        <v>3</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E7" t="n">
+        <v>343</v>
       </c>
       <c r="F7" t="n">
-        <v>87980</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
-      <c r="H7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I7" t="n">
-        <v>343</v>
-      </c>
-      <c r="J7" t="n">
         <v>48</v>
       </c>
     </row>
@@ -712,37 +596,21 @@
       <c r="A8" t="n">
         <v>2</v>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>230730</v>
+      <c r="B8" t="n">
+        <v>4</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
       </c>
       <c r="D8" t="n">
-        <v>4</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E8" t="n">
+        <v>200</v>
       </c>
       <c r="F8" t="n">
-        <v>43400</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
-      <c r="H8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I8" t="n">
-        <v>200</v>
-      </c>
-      <c r="J8" t="n">
         <v>11</v>
       </c>
     </row>
@@ -750,37 +618,21 @@
       <c r="A9" t="n">
         <v>2</v>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>230730</v>
+      <c r="B9" t="n">
+        <v>5</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
       </c>
       <c r="D9" t="n">
-        <v>5</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E9" t="n">
+        <v>155</v>
       </c>
       <c r="F9" t="n">
-        <v>23256</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
-      <c r="H9" t="n">
-        <v>1</v>
-      </c>
-      <c r="I9" t="n">
-        <v>155</v>
-      </c>
-      <c r="J9" t="n">
         <v>154</v>
       </c>
     </row>
@@ -788,37 +640,21 @@
       <c r="A10" t="n">
         <v>3</v>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>87980</v>
+      <c r="B10" t="n">
+        <v>4</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
       </c>
       <c r="D10" t="n">
-        <v>4</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E10" t="n">
+        <v>217</v>
       </c>
       <c r="F10" t="n">
-        <v>43400</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
-        <v>1</v>
-      </c>
-      <c r="I10" t="n">
-        <v>217</v>
-      </c>
-      <c r="J10" t="n">
         <v>11</v>
       </c>
     </row>
@@ -826,37 +662,21 @@
       <c r="A11" t="n">
         <v>4</v>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>43400</v>
+      <c r="B11" t="n">
+        <v>5</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
       </c>
       <c r="D11" t="n">
-        <v>5</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E11" t="n">
+        <v>41</v>
       </c>
       <c r="F11" t="n">
-        <v>23256</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>1</v>
-      </c>
-      <c r="I11" t="n">
-        <v>41</v>
-      </c>
-      <c r="J11" t="n">
         <v>20</v>
       </c>
     </row>
@@ -864,37 +684,21 @@
       <c r="A12" t="n">
         <v>4</v>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>43400</v>
+      <c r="B12" t="n">
+        <v>6</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
       </c>
       <c r="D12" t="n">
-        <v>6</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E12" t="n">
+        <v>174</v>
       </c>
       <c r="F12" t="n">
-        <v>23664</v>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
-      <c r="H12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I12" t="n">
-        <v>174</v>
-      </c>
-      <c r="J12" t="n">
         <v>11</v>
       </c>
     </row>
@@ -902,37 +706,21 @@
       <c r="A13" t="n">
         <v>5</v>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>23256</v>
+      <c r="B13" t="n">
+        <v>6</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
       </c>
       <c r="D13" t="n">
-        <v>6</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E13" t="n">
+        <v>106</v>
       </c>
       <c r="F13" t="n">
-        <v>23664</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
-      <c r="H13" t="n">
-        <v>1</v>
-      </c>
-      <c r="I13" t="n">
-        <v>106</v>
-      </c>
-      <c r="J13" t="n">
         <v>14</v>
       </c>
     </row>

--- a/output/topology_excel/14757.xlsx
+++ b/output/topology_excel/14757.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,22 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Length</t>
+          <t>Length_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Width</t>
+          <t>Width_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Length_2</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Width_2</t>
         </is>
       </c>
     </row>
@@ -481,6 +491,8 @@
       <c r="F2" t="n">
         <v>11</v>
       </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -503,6 +515,8 @@
       <c r="F3" t="n">
         <v>11</v>
       </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -525,6 +539,8 @@
       <c r="F4" t="n">
         <v>11</v>
       </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -547,6 +563,8 @@
       <c r="F5" t="n">
         <v>11</v>
       </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -569,6 +587,8 @@
       <c r="F6" t="n">
         <v>30</v>
       </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -583,13 +603,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E7" t="n">
-        <v>343</v>
+        <v>332</v>
       </c>
       <c r="F7" t="n">
-        <v>48</v>
+        <v>11</v>
+      </c>
+      <c r="G7" t="n">
+        <v>37</v>
+      </c>
+      <c r="H7" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="8">
@@ -613,6 +639,8 @@
       <c r="F8" t="n">
         <v>11</v>
       </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -627,13 +655,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E9" t="n">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="F9" t="n">
-        <v>154</v>
+        <v>17</v>
+      </c>
+      <c r="G9" t="n">
+        <v>144</v>
+      </c>
+      <c r="H9" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="10">
@@ -657,6 +691,8 @@
       <c r="F10" t="n">
         <v>11</v>
       </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -679,6 +715,8 @@
       <c r="F11" t="n">
         <v>20</v>
       </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -701,6 +739,8 @@
       <c r="F12" t="n">
         <v>11</v>
       </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -723,6 +763,8 @@
       <c r="F13" t="n">
         <v>14</v>
       </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
